--- a/Hardware-Designing/_ Deliverables/BOM/Digikey- BOM.xlsx
+++ b/Hardware-Designing/_ Deliverables/BOM/Digikey- BOM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iftik\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\RoomMonitor-Eduardo\Hardware-Designing\_ Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="236">
   <si>
     <t>S. No.</t>
   </si>
@@ -122,18 +122,12 @@
     <t>Bill of Material (BOM) for  Eduardo</t>
   </si>
   <si>
-    <t>C1, C2, C3, C4, C7, C10, C11, C13, C17, C19, C22, C25, C26, C28, C38, C76, C79, C80, C82, C85</t>
-  </si>
-  <si>
     <t>C8, C9</t>
   </si>
   <si>
     <t>C12, C34, C37, C40, C41</t>
   </si>
   <si>
-    <t>C16, C18, C27, C29, C35, C78</t>
-  </si>
-  <si>
     <t>C33</t>
   </si>
   <si>
@@ -408,9 +402,6 @@
   </si>
   <si>
     <t>Vishay Dale Thin Film</t>
-  </si>
-  <si>
-    <t>Tactile Switch SPST-NO Side Actuated Surface Mount, Right Angle</t>
   </si>
   <si>
     <t>SW2</t>
@@ -720,7 +711,30 @@
     <t xml:space="preserve">Total Component Per Board Cost </t>
   </si>
   <si>
-    <t>R1#, R2, R3, R4, R4#, R5, R8, R10, R12, R14, R24, R29, R35, R36, R37, R38, R40, R43, R56, R57, R83, RC2, RC3, RC1,R55</t>
+    <t>C1, C2, C3, C4, C7, C10, C11, C13, C17, C19, C22, C25, C26, C28, C38, C76, C79, C80, C82, C85, C#3, C#5</t>
+  </si>
+  <si>
+    <t>C16, C18, C27, C29, C35, C78, C#4</t>
+  </si>
+  <si>
+    <t>R1#, R2, R3, R4, R4#, R5, R8, R10, R12, R14, R24, R29, R35, R36, R37, R38, R40, R43, R55, R56, R57, R83, RC1, RC2, RC3</t>
+  </si>
+  <si>
+    <t>U15</t>
+  </si>
+  <si>
+    <t>MIC2004-0.5YM5-TR</t>
+  </si>
+  <si>
+    <t>Microchip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IC PWR SWITCH P-CHAN 1:1 SOT23-5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SWITCH TACTILE SPST-NO 0.05A 50V
+</t>
   </si>
 </sst>
 </file>
@@ -839,7 +853,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -1303,6 +1317,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1311,7 +1336,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1360,12 +1385,6 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1421,9 +1440,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1516,12 +1532,6 @@
     <xf numFmtId="166" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1612,6 +1622,18 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1636,17 +1658,41 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1929,21 +1975,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.140625" customWidth="1"/>
-    <col min="5" max="5" width="20.5703125" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.5703125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.140625" style="19" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" style="21" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.7109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="19" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
     <col min="15" max="16" width="14" customWidth="1"/>
@@ -1951,2384 +1997,2424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="102" t="s">
+      <c r="A1" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
-      <c r="K1" s="103"/>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="103"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="103"/>
-      <c r="Q1" s="104"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="102"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="103"/>
     </row>
     <row r="2" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="66" t="s">
+      <c r="D2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="66" t="s">
+      <c r="E2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="66" t="s">
+      <c r="F2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="66" t="s">
-        <v>225</v>
-      </c>
-      <c r="K2" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="L2" s="66" t="s">
-        <v>209</v>
-      </c>
-      <c r="M2" s="66" t="s">
+      <c r="J2" s="63" t="s">
+        <v>222</v>
+      </c>
+      <c r="K2" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="L2" s="63" t="s">
+        <v>206</v>
+      </c>
+      <c r="M2" s="63" t="s">
+        <v>218</v>
+      </c>
+      <c r="N2" s="63" t="s">
+        <v>219</v>
+      </c>
+      <c r="O2" s="63" t="s">
+        <v>220</v>
+      </c>
+      <c r="P2" s="63" t="s">
         <v>221</v>
       </c>
-      <c r="N2" s="66" t="s">
-        <v>222</v>
-      </c>
-      <c r="O2" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="P2" s="66" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q2" s="66" t="s">
+      <c r="Q2" s="63" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23">
+    <row r="3" spans="1:17" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
         <v>1</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="104" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F3" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="G3" s="39" t="s">
+      <c r="C3" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="36" t="s">
         <v>15</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="39" t="s">
+      <c r="I3" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="40">
-        <v>20</v>
-      </c>
-      <c r="K3" s="40">
+      <c r="J3" s="37">
+        <v>22</v>
+      </c>
+      <c r="K3" s="37">
         <f>J3*5</f>
-        <v>100</v>
-      </c>
-      <c r="L3" s="41" t="s">
-        <v>210</v>
+        <v>110</v>
+      </c>
+      <c r="L3" s="38" t="s">
+        <v>207</v>
       </c>
       <c r="M3" s="15">
         <v>4.5999999999999999E-2</v>
       </c>
-      <c r="N3" s="42">
+      <c r="N3" s="39">
         <f>M3*J3</f>
-        <v>0.91999999999999993</v>
-      </c>
-      <c r="O3" s="60">
+        <v>1.012</v>
+      </c>
+      <c r="O3" s="57">
         <v>2.1399999999999999E-2</v>
       </c>
-      <c r="P3" s="68">
+      <c r="P3" s="65">
         <f>O3*K3</f>
-        <v>2.1399999999999997</v>
+        <v>2.3540000000000001</v>
       </c>
       <c r="Q3" s="11"/>
     </row>
     <row r="4" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23">
+      <c r="A4" s="21">
         <v>2</v>
       </c>
-      <c r="B4" s="106"/>
-      <c r="C4" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="27" t="s">
+      <c r="B4" s="105"/>
+      <c r="C4" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>55</v>
+        <v>42</v>
+      </c>
+      <c r="G4" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="26">
         <v>2</v>
       </c>
-      <c r="K4" s="28">
-        <f t="shared" ref="K4:K46" si="0">J4*5</f>
+      <c r="K4" s="26">
+        <f t="shared" ref="K4:K47" si="0">J4*5</f>
         <v>10</v>
       </c>
-      <c r="L4" s="34" t="s">
-        <v>210</v>
+      <c r="L4" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M4" s="16">
         <v>0.36</v>
       </c>
-      <c r="N4" s="36">
-        <f t="shared" ref="N4:N45" si="1">M4*J4</f>
+      <c r="N4" s="34">
+        <f t="shared" ref="N4:N46" si="1">M4*J4</f>
         <v>0.72</v>
       </c>
-      <c r="O4" s="61">
+      <c r="O4" s="58">
         <v>0.25900000000000001</v>
       </c>
-      <c r="P4" s="69">
-        <f t="shared" ref="P4:P46" si="2">O4*K4</f>
+      <c r="P4" s="66">
+        <f t="shared" ref="P4:P47" si="2">O4*K4</f>
         <v>2.59</v>
       </c>
       <c r="Q4" s="12"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23">
+      <c r="A5" s="21">
         <v>3</v>
       </c>
-      <c r="B5" s="106"/>
-      <c r="C5" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D5" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>53</v>
+      <c r="B5" s="105"/>
+      <c r="C5" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>51</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>54</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="J5" s="28">
+      <c r="I5" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" s="26">
         <v>5</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="26">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="L5" s="34" t="s">
-        <v>210</v>
+      <c r="L5" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M5" s="16">
         <v>0.82</v>
       </c>
-      <c r="N5" s="36">
+      <c r="N5" s="34">
         <f t="shared" si="1"/>
         <v>4.0999999999999996</v>
       </c>
-      <c r="O5" s="61">
+      <c r="O5" s="58">
         <v>0.60699999999999998</v>
       </c>
-      <c r="P5" s="69">
+      <c r="P5" s="66">
         <f t="shared" si="2"/>
         <v>15.174999999999999</v>
       </c>
       <c r="Q5" s="12"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23">
+      <c r="A6" s="21">
         <v>4</v>
       </c>
-      <c r="B6" s="106"/>
-      <c r="C6" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>54</v>
+      <c r="B6" s="105"/>
+      <c r="C6" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>57</v>
+        <v>48</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>55</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="28">
-        <v>6</v>
-      </c>
-      <c r="K6" s="28">
+      <c r="J6" s="26">
+        <v>7</v>
+      </c>
+      <c r="K6" s="26">
         <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="L6" s="34" t="s">
-        <v>210</v>
+        <v>35</v>
+      </c>
+      <c r="L6" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M6" s="16">
         <v>0.1</v>
       </c>
-      <c r="N6" s="36">
+      <c r="N6" s="34">
         <f t="shared" si="1"/>
-        <v>0.60000000000000009</v>
-      </c>
-      <c r="O6" s="61">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="O6" s="58">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="P6" s="69">
+      <c r="P6" s="66">
         <f t="shared" si="2"/>
-        <v>1.71</v>
+        <v>1.9950000000000001</v>
       </c>
       <c r="Q6" s="12"/>
     </row>
     <row r="7" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23">
+      <c r="A7" s="21">
         <v>5</v>
       </c>
-      <c r="B7" s="106"/>
-      <c r="C7" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="27" t="s">
+      <c r="B7" s="105"/>
+      <c r="C7" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="25" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G7" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="25" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="28">
+      <c r="I7" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="26">
         <v>1</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L7" s="34" t="s">
-        <v>210</v>
+      <c r="L7" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M7" s="16">
         <v>0.11</v>
       </c>
-      <c r="N7" s="36">
+      <c r="N7" s="34">
         <f t="shared" si="1"/>
         <v>0.11</v>
       </c>
-      <c r="O7" s="61">
+      <c r="O7" s="58">
         <v>0.11</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="66">
         <f t="shared" si="2"/>
         <v>0.55000000000000004</v>
       </c>
       <c r="Q7" s="12"/>
     </row>
     <row r="8" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="A8" s="21">
         <v>6</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>54</v>
+      <c r="B8" s="106"/>
+      <c r="C8" s="40" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>52</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="45" t="s">
-        <v>58</v>
+        <v>50</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>56</v>
       </c>
       <c r="H8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="J8" s="46">
+      <c r="I8" s="42" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="43">
         <v>1</v>
       </c>
-      <c r="K8" s="46">
+      <c r="K8" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L8" s="47" t="s">
-        <v>210</v>
+      <c r="L8" s="44" t="s">
+        <v>207</v>
       </c>
       <c r="M8" s="17">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N8" s="48">
+      <c r="N8" s="45">
         <f t="shared" si="1"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="O8" s="62">
+      <c r="O8" s="59">
         <v>0.28000000000000003</v>
       </c>
-      <c r="P8" s="73">
+      <c r="P8" s="68">
         <f t="shared" si="2"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23">
+      <c r="A9" s="21">
         <v>7</v>
       </c>
-      <c r="B9" s="105" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="37" t="s">
+      <c r="B9" s="104" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="E9" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="G9" s="39" t="s">
+      <c r="G9" s="36" t="s">
         <v>14</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J9" s="40">
+        <v>209</v>
+      </c>
+      <c r="J9" s="37">
         <v>1</v>
       </c>
-      <c r="K9" s="40">
+      <c r="K9" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L9" s="70" t="s">
-        <v>227</v>
+      <c r="L9" s="32" t="s">
+        <v>224</v>
       </c>
       <c r="M9" s="15">
         <v>0.221</v>
       </c>
-      <c r="N9" s="42">
+      <c r="N9" s="39">
         <f t="shared" si="1"/>
         <v>0.221</v>
       </c>
-      <c r="O9" s="60">
+      <c r="O9" s="57">
         <v>0.221</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="39">
         <f t="shared" si="2"/>
         <v>1.105</v>
       </c>
       <c r="Q9" s="11"/>
     </row>
     <row r="10" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23">
+      <c r="A10" s="21">
         <v>8</v>
       </c>
-      <c r="B10" s="107"/>
-      <c r="C10" s="43" t="s">
+      <c r="B10" s="106"/>
+      <c r="C10" s="40" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="F10" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="E10" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" s="45" t="s">
+      <c r="G10" s="42" t="s">
         <v>11</v>
       </c>
       <c r="H10" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J10" s="46">
+        <v>209</v>
+      </c>
+      <c r="J10" s="43">
         <v>1</v>
       </c>
-      <c r="K10" s="46">
+      <c r="K10" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L10" s="47" t="s">
-        <v>210</v>
+      <c r="L10" s="44" t="s">
+        <v>207</v>
       </c>
       <c r="M10" s="17">
         <v>0.13</v>
       </c>
-      <c r="N10" s="48">
+      <c r="N10" s="45">
         <f t="shared" si="1"/>
         <v>0.13</v>
       </c>
-      <c r="O10" s="62">
+      <c r="O10" s="59">
         <v>0.13</v>
       </c>
-      <c r="P10" s="73">
+      <c r="P10" s="68">
         <f t="shared" si="2"/>
         <v>0.65</v>
       </c>
       <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23">
+      <c r="A11" s="21">
         <v>9</v>
       </c>
-      <c r="B11" s="74" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="75" t="s">
+      <c r="B11" s="69" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="70" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="76" t="s">
+      <c r="G11" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="77" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="78" t="s">
+      <c r="H11" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="79" t="s">
-        <v>212</v>
-      </c>
-      <c r="J11" s="80">
+      <c r="I11" s="74" t="s">
+        <v>209</v>
+      </c>
+      <c r="J11" s="75">
         <v>1</v>
       </c>
-      <c r="K11" s="80">
+      <c r="K11" s="75">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L11" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="M11" s="82">
+      <c r="L11" s="76" t="s">
+        <v>207</v>
+      </c>
+      <c r="M11" s="77">
         <v>0.5</v>
       </c>
-      <c r="N11" s="83">
+      <c r="N11" s="78">
         <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
-      <c r="O11" s="84">
+      <c r="O11" s="79">
         <v>0.5</v>
       </c>
-      <c r="P11" s="83">
+      <c r="P11" s="78">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
-      <c r="Q11" s="85"/>
+      <c r="Q11" s="80"/>
     </row>
     <row r="12" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="23">
+      <c r="A12" s="21">
         <v>10</v>
       </c>
-      <c r="B12" s="105" t="s">
-        <v>208</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D12" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" s="39" t="s">
-        <v>106</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>122</v>
+      <c r="B12" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="46" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="F12" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>120</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="40">
+        <v>209</v>
+      </c>
+      <c r="J12" s="37">
         <v>2</v>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L12" s="41" t="s">
-        <v>210</v>
+      <c r="L12" s="38" t="s">
+        <v>207</v>
       </c>
       <c r="M12" s="15">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N12" s="42">
+      <c r="N12" s="39">
         <f t="shared" si="1"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="O12" s="60">
+      <c r="O12" s="57">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="39">
         <f t="shared" si="2"/>
         <v>0.97</v>
       </c>
       <c r="Q12" s="11"/>
     </row>
     <row r="13" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23">
+      <c r="A13" s="21">
         <v>11</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>123</v>
+      <c r="B13" s="105"/>
+      <c r="C13" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>121</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J13" s="28">
+        <v>209</v>
+      </c>
+      <c r="J13" s="26">
         <v>3</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="L13" s="34" t="s">
-        <v>210</v>
+      <c r="L13" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M13" s="16">
         <v>0.28000000000000003</v>
       </c>
-      <c r="N13" s="36">
+      <c r="N13" s="34">
         <f t="shared" si="1"/>
         <v>0.84000000000000008</v>
       </c>
-      <c r="O13" s="61">
+      <c r="O13" s="58">
         <v>0.189</v>
       </c>
-      <c r="P13" s="69">
+      <c r="P13" s="66">
         <f t="shared" si="2"/>
         <v>2.835</v>
       </c>
       <c r="Q13" s="12"/>
     </row>
     <row r="14" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23">
+      <c r="A14" s="21">
         <v>12</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="26" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>122</v>
+      <c r="B14" s="105"/>
+      <c r="C14" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>120</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J14" s="28">
+        <v>209</v>
+      </c>
+      <c r="J14" s="26">
         <v>1</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L14" s="34" t="s">
-        <v>210</v>
+      <c r="L14" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M14" s="16">
         <v>0.47</v>
       </c>
-      <c r="N14" s="36">
+      <c r="N14" s="34">
         <f t="shared" si="1"/>
         <v>0.47</v>
       </c>
-      <c r="O14" s="61">
+      <c r="O14" s="58">
         <v>0.47</v>
       </c>
-      <c r="P14" s="69">
+      <c r="P14" s="66">
         <f t="shared" si="2"/>
         <v>2.3499999999999996</v>
       </c>
       <c r="Q14" s="12"/>
     </row>
     <row r="15" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23">
+      <c r="A15" s="21">
         <v>13</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="43" t="s">
-        <v>77</v>
-      </c>
-      <c r="D15" s="44" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="F15" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="45" t="s">
-        <v>124</v>
+      <c r="B15" s="106"/>
+      <c r="C15" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>122</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>24</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="46">
+        <v>209</v>
+      </c>
+      <c r="J15" s="43">
         <v>1</v>
       </c>
-      <c r="K15" s="46">
+      <c r="K15" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L15" s="47" t="s">
-        <v>210</v>
+      <c r="L15" s="44" t="s">
+        <v>207</v>
       </c>
       <c r="M15" s="17">
         <v>0.36</v>
       </c>
-      <c r="N15" s="48">
+      <c r="N15" s="45">
         <f t="shared" si="1"/>
         <v>0.36</v>
       </c>
-      <c r="O15" s="62">
+      <c r="O15" s="59">
         <v>0.36</v>
       </c>
-      <c r="P15" s="73">
+      <c r="P15" s="68">
         <f t="shared" si="2"/>
         <v>1.7999999999999998</v>
       </c>
       <c r="Q15" s="14"/>
     </row>
     <row r="16" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23">
+      <c r="A16" s="21">
         <v>14</v>
       </c>
-      <c r="B16" s="105" t="s">
+      <c r="B16" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="49" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="G16" s="39" t="s">
+      <c r="C16" s="35" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="F16" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="36" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="39" t="s">
-        <v>195</v>
-      </c>
-      <c r="J16" s="40">
+      <c r="I16" s="36" t="s">
+        <v>192</v>
+      </c>
+      <c r="J16" s="37">
         <v>2</v>
       </c>
-      <c r="K16" s="40">
+      <c r="K16" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L16" s="41" t="s">
-        <v>210</v>
+      <c r="L16" s="38" t="s">
+        <v>207</v>
       </c>
       <c r="M16" s="15">
         <v>0.12</v>
       </c>
-      <c r="N16" s="42">
+      <c r="N16" s="39">
         <f t="shared" si="1"/>
         <v>0.24</v>
       </c>
-      <c r="O16" s="60">
+      <c r="O16" s="57">
         <v>0.108</v>
       </c>
-      <c r="P16" s="42">
+      <c r="P16" s="39">
         <f t="shared" si="2"/>
         <v>1.08</v>
       </c>
       <c r="Q16" s="11"/>
     </row>
     <row r="17" spans="1:17" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="23">
+      <c r="A17" s="21">
         <v>15</v>
       </c>
-      <c r="B17" s="106"/>
-      <c r="C17" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="B17" s="105"/>
+      <c r="C17" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>109</v>
+      </c>
+      <c r="G17" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I17" s="27" t="s">
-        <v>196</v>
-      </c>
-      <c r="J17" s="28">
+      <c r="I17" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="26">
         <v>25</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="26">
         <v>125</v>
       </c>
-      <c r="L17" s="34" t="s">
-        <v>210</v>
+      <c r="L17" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M17" s="16">
         <v>0.108</v>
       </c>
-      <c r="N17" s="36">
+      <c r="N17" s="34">
         <f t="shared" si="1"/>
         <v>2.7</v>
       </c>
-      <c r="O17" s="61">
+      <c r="O17" s="58">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="P17" s="69">
+      <c r="P17" s="66">
         <f t="shared" si="2"/>
         <v>5.1749999999999998</v>
       </c>
       <c r="Q17" s="12"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23">
+      <c r="A18" s="21">
         <v>16</v>
       </c>
-      <c r="B18" s="106"/>
-      <c r="C18" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>125</v>
+      <c r="B18" s="105"/>
+      <c r="C18" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>123</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I18" s="27" t="s">
+      <c r="I18" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="26">
         <v>1</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L18" s="34" t="s">
-        <v>210</v>
+      <c r="L18" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M18" s="16">
         <v>0.26</v>
       </c>
-      <c r="N18" s="36">
+      <c r="N18" s="34">
         <f t="shared" si="1"/>
         <v>0.26</v>
       </c>
-      <c r="O18" s="61">
+      <c r="O18" s="58">
         <v>0.26</v>
       </c>
-      <c r="P18" s="69">
+      <c r="P18" s="66">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="Q18" s="12"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23">
+      <c r="A19" s="21">
         <v>17</v>
       </c>
-      <c r="B19" s="106"/>
-      <c r="C19" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E19" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="B19" s="105"/>
+      <c r="C19" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="G19" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I19" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="J19" s="28">
+      <c r="I19" s="25" t="s">
+        <v>194</v>
+      </c>
+      <c r="J19" s="26">
         <v>1</v>
       </c>
-      <c r="K19" s="28">
+      <c r="K19" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L19" s="34" t="s">
-        <v>210</v>
+      <c r="L19" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M19" s="16">
         <v>0.12</v>
       </c>
-      <c r="N19" s="36">
+      <c r="N19" s="34">
         <f t="shared" si="1"/>
         <v>0.12</v>
       </c>
-      <c r="O19" s="61">
+      <c r="O19" s="58">
         <v>0.12</v>
       </c>
-      <c r="P19" s="69">
+      <c r="P19" s="66">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="Q19" s="12"/>
     </row>
     <row r="20" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23">
+      <c r="A20" s="21">
         <v>18</v>
       </c>
-      <c r="B20" s="106"/>
-      <c r="C20" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G20" s="27" t="s">
+      <c r="B20" s="105"/>
+      <c r="C20" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G20" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I20" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="J20" s="28">
+      <c r="I20" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" s="26">
         <v>1</v>
       </c>
-      <c r="K20" s="28">
+      <c r="K20" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L20" s="34" t="s">
-        <v>210</v>
+      <c r="L20" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M20" s="16">
         <v>0.12</v>
       </c>
-      <c r="N20" s="36">
+      <c r="N20" s="34">
         <f>M20*J20</f>
         <v>0.12</v>
       </c>
-      <c r="O20" s="61">
+      <c r="O20" s="58">
         <v>0.12</v>
       </c>
-      <c r="P20" s="69">
+      <c r="P20" s="66">
         <f t="shared" si="2"/>
         <v>0.6</v>
       </c>
       <c r="Q20" s="12"/>
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23">
+      <c r="A21" s="21">
         <v>19</v>
       </c>
-      <c r="B21" s="106"/>
-      <c r="C21" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F21" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>126</v>
+      <c r="B21" s="105"/>
+      <c r="C21" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="27" t="s">
-        <v>199</v>
-      </c>
-      <c r="J21" s="28">
+      <c r="I21" s="25" t="s">
+        <v>196</v>
+      </c>
+      <c r="J21" s="26">
         <v>1</v>
       </c>
-      <c r="K21" s="28">
+      <c r="K21" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L21" s="34" t="s">
-        <v>210</v>
+      <c r="L21" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M21" s="16">
         <v>0.26</v>
       </c>
-      <c r="N21" s="36">
+      <c r="N21" s="34">
         <f t="shared" si="1"/>
         <v>0.26</v>
       </c>
-      <c r="O21" s="61">
+      <c r="O21" s="58">
         <v>0.26</v>
       </c>
-      <c r="P21" s="69">
+      <c r="P21" s="66">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="Q21" s="12"/>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23">
+      <c r="A22" s="21">
         <v>20</v>
       </c>
-      <c r="B22" s="106"/>
-      <c r="C22" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="E22" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="F22" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="G22" s="27" t="s">
+      <c r="B22" s="105"/>
+      <c r="C22" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F22" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I22" s="27" t="s">
-        <v>200</v>
-      </c>
-      <c r="J22" s="28">
+      <c r="I22" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="J22" s="26">
         <v>1</v>
       </c>
-      <c r="K22" s="28">
+      <c r="K22" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L22" s="34" t="s">
-        <v>210</v>
+      <c r="L22" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M22" s="16">
         <v>0.1</v>
       </c>
-      <c r="N22" s="36">
+      <c r="N22" s="34">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="O22" s="61">
+      <c r="O22" s="58">
         <v>0.1</v>
       </c>
-      <c r="P22" s="69">
+      <c r="P22" s="66">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="Q22" s="12"/>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23">
+      <c r="A23" s="21">
         <v>21</v>
       </c>
-      <c r="B23" s="106"/>
-      <c r="C23" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="B23" s="105"/>
+      <c r="C23" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="27" t="s">
-        <v>201</v>
-      </c>
-      <c r="J23" s="28">
+      <c r="I23" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="J23" s="26">
         <v>1</v>
       </c>
-      <c r="K23" s="28">
+      <c r="K23" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L23" s="34" t="s">
-        <v>210</v>
+      <c r="L23" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M23" s="16">
         <v>0.1</v>
       </c>
-      <c r="N23" s="36">
+      <c r="N23" s="34">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="O23" s="61">
+      <c r="O23" s="58">
         <v>0.1</v>
       </c>
-      <c r="P23" s="69">
+      <c r="P23" s="66">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="Q23" s="12"/>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="23">
+      <c r="A24" s="21">
         <v>22</v>
       </c>
-      <c r="B24" s="106"/>
-      <c r="C24" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="E24" s="27" t="s">
+      <c r="B24" s="105"/>
+      <c r="C24" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="27" t="s">
+      <c r="F24" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I24" s="27" t="s">
-        <v>202</v>
-      </c>
-      <c r="J24" s="28">
+      <c r="I24" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="J24" s="26">
         <v>1</v>
       </c>
-      <c r="K24" s="28">
+      <c r="K24" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L24" s="34" t="s">
-        <v>210</v>
+      <c r="L24" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M24" s="16">
         <v>0.1</v>
       </c>
-      <c r="N24" s="36">
+      <c r="N24" s="34">
         <f t="shared" si="1"/>
         <v>0.1</v>
       </c>
-      <c r="O24" s="61">
+      <c r="O24" s="58">
         <v>0.1</v>
       </c>
-      <c r="P24" s="69">
+      <c r="P24" s="66">
         <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="Q24" s="12"/>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="23">
+      <c r="A25" s="21">
         <v>23</v>
       </c>
-      <c r="B25" s="106"/>
-      <c r="C25" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" s="27" t="s">
+      <c r="B25" s="105"/>
+      <c r="C25" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="27" t="s">
-        <v>119</v>
-      </c>
-      <c r="G25" s="27" t="s">
+      <c r="F25" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G25" s="25" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="J25" s="28">
+      <c r="I25" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="J25" s="26">
         <v>2</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L25" s="34" t="s">
-        <v>210</v>
+      <c r="L25" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M25" s="16">
         <v>0.1</v>
       </c>
-      <c r="N25" s="36">
+      <c r="N25" s="34">
         <f t="shared" si="1"/>
         <v>0.2</v>
       </c>
-      <c r="O25" s="61">
+      <c r="O25" s="58">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="P25" s="69">
+      <c r="P25" s="66">
         <f t="shared" si="2"/>
         <v>0.66</v>
       </c>
       <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="23">
+      <c r="A26" s="21">
         <v>24</v>
       </c>
-      <c r="B26" s="106"/>
-      <c r="C26" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>120</v>
-      </c>
-      <c r="G26" s="27" t="s">
+      <c r="B26" s="105"/>
+      <c r="C26" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="25" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I26" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="J26" s="28">
+      <c r="I26" s="25" t="s">
+        <v>201</v>
+      </c>
+      <c r="J26" s="26">
         <v>2</v>
       </c>
-      <c r="K26" s="28">
+      <c r="K26" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L26" s="34" t="s">
-        <v>213</v>
+      <c r="L26" s="32" t="s">
+        <v>210</v>
       </c>
       <c r="M26" s="16">
         <v>0.12</v>
       </c>
-      <c r="N26" s="36">
+      <c r="N26" s="34">
         <f t="shared" si="1"/>
         <v>0.24</v>
       </c>
-      <c r="O26" s="61">
+      <c r="O26" s="58">
         <v>0.108</v>
       </c>
-      <c r="P26" s="69">
+      <c r="P26" s="66">
         <f t="shared" si="2"/>
         <v>1.08</v>
       </c>
       <c r="Q26" s="12"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="23">
+      <c r="A27" s="21">
         <v>25</v>
       </c>
-      <c r="B27" s="107"/>
-      <c r="C27" s="43" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="44" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="G27" s="45" t="s">
-        <v>127</v>
+      <c r="B27" s="106"/>
+      <c r="C27" s="40" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>103</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>119</v>
+      </c>
+      <c r="G27" s="42" t="s">
+        <v>125</v>
       </c>
       <c r="H27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="J27" s="46">
+      <c r="I27" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="J27" s="43">
         <v>1</v>
       </c>
-      <c r="K27" s="46">
+      <c r="K27" s="43">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L27" s="47" t="s">
-        <v>210</v>
+      <c r="L27" s="44" t="s">
+        <v>207</v>
       </c>
       <c r="M27" s="17">
         <v>0.84</v>
       </c>
-      <c r="N27" s="48">
+      <c r="N27" s="45">
         <f t="shared" si="1"/>
         <v>0.84</v>
       </c>
-      <c r="O27" s="62">
+      <c r="O27" s="59">
         <v>0.84</v>
       </c>
-      <c r="P27" s="73">
+      <c r="P27" s="68">
         <f t="shared" si="2"/>
         <v>4.2</v>
       </c>
       <c r="Q27" s="14"/>
     </row>
-    <row r="28" spans="1:17" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="23">
+    <row r="28" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21">
         <v>26</v>
       </c>
-      <c r="B28" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="75" t="s">
+      <c r="B28" s="69" t="s">
+        <v>180</v>
+      </c>
+      <c r="C28" s="120" t="s">
+        <v>235</v>
+      </c>
+      <c r="D28" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="72" t="s">
+        <v>127</v>
+      </c>
+      <c r="G28" s="72" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="76" t="s">
-        <v>129</v>
-      </c>
-      <c r="E28" s="77" t="s">
-        <v>27</v>
-      </c>
-      <c r="F28" s="77" t="s">
-        <v>130</v>
-      </c>
-      <c r="G28" s="77" t="s">
-        <v>131</v>
-      </c>
-      <c r="H28" s="78" t="s">
+      <c r="H28" s="73" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="79"/>
-      <c r="J28" s="86">
+      <c r="I28" s="74"/>
+      <c r="J28" s="81">
         <v>1</v>
       </c>
-      <c r="K28" s="80">
+      <c r="K28" s="75">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L28" s="87" t="s">
-        <v>210</v>
-      </c>
-      <c r="M28" s="82">
+      <c r="L28" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="M28" s="77">
         <v>0.61</v>
       </c>
-      <c r="N28" s="83">
+      <c r="N28" s="78">
         <f t="shared" si="1"/>
         <v>0.61</v>
       </c>
-      <c r="O28" s="84">
+      <c r="O28" s="79">
         <v>0.61</v>
       </c>
-      <c r="P28" s="83">
+      <c r="P28" s="78">
         <f t="shared" si="2"/>
         <v>3.05</v>
       </c>
-      <c r="Q28" s="85"/>
-    </row>
-    <row r="29" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="23">
+      <c r="Q28" s="80"/>
+    </row>
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="110">
         <v>27</v>
       </c>
-      <c r="B29" s="105" t="s">
-        <v>184</v>
-      </c>
-      <c r="C29" s="58" t="s">
-        <v>215</v>
-      </c>
-      <c r="D29" s="49" t="s">
+      <c r="B29" s="104" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" s="55" t="s">
+        <v>212</v>
+      </c>
+      <c r="D29" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="E29" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>168</v>
+      <c r="E29" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="F29" s="36" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>165</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I29" s="4"/>
-      <c r="J29" s="40">
+      <c r="J29" s="37">
         <v>1</v>
       </c>
-      <c r="K29" s="40">
+      <c r="K29" s="37">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L29" s="41" t="s">
-        <v>210</v>
+      <c r="L29" s="38" t="s">
+        <v>207</v>
       </c>
       <c r="M29" s="15">
         <v>1.98</v>
       </c>
-      <c r="N29" s="42">
+      <c r="N29" s="39">
         <f t="shared" si="1"/>
         <v>1.98</v>
       </c>
-      <c r="O29" s="60">
+      <c r="O29" s="57">
         <v>1.98</v>
       </c>
-      <c r="P29" s="42">
+      <c r="P29" s="39">
         <f t="shared" si="2"/>
         <v>9.9</v>
       </c>
       <c r="Q29" s="11"/>
     </row>
-    <row r="30" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="23">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="110">
         <v>28</v>
       </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="26" t="s">
+      <c r="B30" s="105"/>
+      <c r="C30" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="F30" s="27" t="s">
-        <v>156</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>123</v>
+      <c r="E30" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="25" t="s">
+        <v>121</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J30" s="28">
+        <v>209</v>
+      </c>
+      <c r="J30" s="26">
         <v>1</v>
       </c>
-      <c r="K30" s="28">
+      <c r="K30" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L30" s="34" t="s">
-        <v>210</v>
+      <c r="L30" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M30" s="16">
         <v>0.54</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="34">
         <f t="shared" si="1"/>
         <v>0.54</v>
       </c>
-      <c r="O30" s="61">
+      <c r="O30" s="58">
         <v>0.54</v>
       </c>
-      <c r="P30" s="69">
+      <c r="P30" s="66">
         <f t="shared" si="2"/>
         <v>2.7</v>
       </c>
       <c r="Q30" s="12"/>
     </row>
-    <row r="31" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="110">
         <v>29</v>
       </c>
-      <c r="B31" s="106"/>
-      <c r="C31" s="25" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="F31" s="27" t="s">
-        <v>157</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>168</v>
+      <c r="B31" s="105"/>
+      <c r="C31" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="G31" s="25" t="s">
+        <v>165</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J31" s="28">
+        <v>209</v>
+      </c>
+      <c r="J31" s="26">
         <v>2</v>
       </c>
-      <c r="K31" s="28">
+      <c r="K31" s="26">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="L31" s="34" t="s">
-        <v>210</v>
+      <c r="L31" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M31" s="16">
         <v>1.64</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="34">
         <f t="shared" si="1"/>
         <v>3.28</v>
       </c>
-      <c r="O31" s="61">
+      <c r="O31" s="58">
         <v>1.472</v>
       </c>
-      <c r="P31" s="69">
+      <c r="P31" s="66">
         <f t="shared" si="2"/>
         <v>14.719999999999999</v>
       </c>
       <c r="Q31" s="12"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="23">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="110">
         <v>30</v>
       </c>
-      <c r="B32" s="106"/>
-      <c r="C32" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D32" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E32" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="F32" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>168</v>
+      <c r="B32" s="105"/>
+      <c r="C32" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="F32" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="G32" s="25" t="s">
+        <v>165</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J32" s="28">
+        <v>209</v>
+      </c>
+      <c r="J32" s="26">
         <v>1</v>
       </c>
-      <c r="K32" s="28">
+      <c r="K32" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L32" s="34" t="s">
-        <v>210</v>
+      <c r="L32" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M32" s="16">
         <v>0.6</v>
       </c>
-      <c r="N32" s="36">
+      <c r="N32" s="34">
         <f t="shared" si="1"/>
         <v>0.6</v>
       </c>
-      <c r="O32" s="61">
+      <c r="O32" s="58">
         <v>0.6</v>
       </c>
-      <c r="P32" s="69">
+      <c r="P32" s="66">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="Q32" s="12"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="23">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="110">
         <v>31</v>
       </c>
-      <c r="B33" s="106"/>
-      <c r="C33" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="D33" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="E33" s="27" t="s">
-        <v>176</v>
-      </c>
-      <c r="F33" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>169</v>
+      <c r="B33" s="105"/>
+      <c r="C33" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="G33" s="25" t="s">
+        <v>166</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J33" s="28">
+        <v>209</v>
+      </c>
+      <c r="J33" s="26">
         <v>1</v>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L33" s="71" t="s">
-        <v>228</v>
+      <c r="L33" s="32" t="s">
+        <v>225</v>
       </c>
       <c r="M33" s="16">
         <v>2.76</v>
       </c>
-      <c r="N33" s="36">
+      <c r="N33" s="34">
         <f t="shared" si="1"/>
         <v>2.76</v>
       </c>
-      <c r="O33" s="61">
+      <c r="O33" s="58">
         <v>2.76</v>
       </c>
-      <c r="P33" s="69">
+      <c r="P33" s="66">
         <f t="shared" si="2"/>
         <v>13.799999999999999</v>
       </c>
       <c r="Q33" s="12"/>
     </row>
     <row r="34" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="23">
+      <c r="A34" s="110">
         <v>32</v>
       </c>
-      <c r="B34" s="106"/>
-      <c r="C34" s="25" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="E34" s="27" t="s">
+      <c r="B34" s="105"/>
+      <c r="C34" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F34" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="G34" s="27" t="s">
-        <v>170</v>
+      <c r="F34" s="25" t="s">
+        <v>157</v>
+      </c>
+      <c r="G34" s="25" t="s">
+        <v>167</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J34" s="28">
+        <v>209</v>
+      </c>
+      <c r="J34" s="26">
         <v>1</v>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L34" s="34" t="s">
-        <v>210</v>
+      <c r="L34" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M34" s="16">
         <v>0.93</v>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="34">
         <f t="shared" si="1"/>
         <v>0.93</v>
       </c>
-      <c r="O34" s="61">
+      <c r="O34" s="58">
         <v>0.93</v>
       </c>
-      <c r="P34" s="69">
+      <c r="P34" s="66">
         <f t="shared" si="2"/>
         <v>4.6500000000000004</v>
       </c>
       <c r="Q34" s="12"/>
     </row>
     <row r="35" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23">
+      <c r="A35" s="110">
         <v>33</v>
       </c>
-      <c r="B35" s="106"/>
-      <c r="C35" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="D35" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>179</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>171</v>
+      <c r="B35" s="105"/>
+      <c r="C35" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>158</v>
+      </c>
+      <c r="G35" s="25" t="s">
+        <v>168</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J35" s="28">
+        <v>209</v>
+      </c>
+      <c r="J35" s="26">
         <v>1</v>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L35" s="34" t="s">
-        <v>210</v>
+      <c r="L35" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M35" s="16">
         <v>3.37</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="34">
         <f t="shared" si="1"/>
         <v>3.37</v>
       </c>
-      <c r="O35" s="61">
+      <c r="O35" s="58">
         <v>3.37</v>
       </c>
-      <c r="P35" s="69">
+      <c r="P35" s="66">
         <f t="shared" si="2"/>
         <v>16.850000000000001</v>
       </c>
       <c r="Q35" s="12"/>
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="23">
+      <c r="A36" s="110">
         <v>34</v>
       </c>
-      <c r="B36" s="106"/>
-      <c r="C36" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" s="27" t="s">
+      <c r="B36" s="105"/>
+      <c r="C36" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F36" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="G36" s="27" t="s">
-        <v>172</v>
+      <c r="F36" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G36" s="25" t="s">
+        <v>169</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J36" s="28">
+        <v>209</v>
+      </c>
+      <c r="J36" s="26">
         <v>1</v>
       </c>
-      <c r="K36" s="28">
+      <c r="K36" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L36" s="34" t="s">
-        <v>210</v>
+      <c r="L36" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M36" s="16">
         <v>4.5</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="34">
         <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
-      <c r="O36" s="61">
+      <c r="O36" s="58">
         <v>4.6500000000000004</v>
       </c>
-      <c r="P36" s="69">
+      <c r="P36" s="66">
         <f t="shared" si="2"/>
         <v>23.25</v>
       </c>
       <c r="Q36" s="12"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="23">
+      <c r="A37" s="110">
         <v>35</v>
       </c>
-      <c r="B37" s="106"/>
-      <c r="C37" s="25" t="s">
-        <v>145</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>146</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="F37" s="27" t="s">
-        <v>163</v>
-      </c>
-      <c r="G37" s="27" t="s">
-        <v>168</v>
+      <c r="B37" s="105"/>
+      <c r="C37" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="G37" s="25" t="s">
+        <v>165</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J37" s="28">
+        <v>209</v>
+      </c>
+      <c r="J37" s="26">
         <v>1</v>
       </c>
-      <c r="K37" s="28">
+      <c r="K37" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L37" s="34" t="s">
-        <v>210</v>
+      <c r="L37" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M37" s="16">
         <v>1.26</v>
       </c>
-      <c r="N37" s="36">
+      <c r="N37" s="34">
         <f t="shared" si="1"/>
         <v>1.26</v>
       </c>
-      <c r="O37" s="61">
+      <c r="O37" s="58">
         <v>1.26</v>
       </c>
-      <c r="P37" s="69">
+      <c r="P37" s="66">
         <f t="shared" si="2"/>
         <v>6.3</v>
       </c>
       <c r="Q37" s="12"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="23">
+      <c r="A38" s="110">
         <v>36</v>
       </c>
-      <c r="B38" s="106"/>
-      <c r="C38" s="25" t="s">
-        <v>147</v>
-      </c>
-      <c r="D38" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="F38" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="G38" s="27" t="s">
-        <v>168</v>
+      <c r="B38" s="105"/>
+      <c r="C38" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G38" s="25" t="s">
+        <v>165</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J38" s="28">
+        <v>209</v>
+      </c>
+      <c r="J38" s="26">
         <v>1</v>
       </c>
-      <c r="K38" s="28">
+      <c r="K38" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L38" s="34" t="s">
-        <v>210</v>
+      <c r="L38" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M38" s="16">
         <v>2.48</v>
       </c>
-      <c r="N38" s="36">
+      <c r="N38" s="34">
         <f t="shared" si="1"/>
         <v>2.48</v>
       </c>
-      <c r="O38" s="61">
+      <c r="O38" s="58">
         <v>2.48</v>
       </c>
-      <c r="P38" s="69">
+      <c r="P38" s="66">
         <f t="shared" si="2"/>
         <v>12.4</v>
       </c>
       <c r="Q38" s="12"/>
     </row>
     <row r="39" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="23">
+      <c r="A39" s="110">
         <v>37</v>
       </c>
-      <c r="B39" s="106"/>
-      <c r="C39" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D39" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>177</v>
-      </c>
-      <c r="F39" s="27" t="s">
+      <c r="B39" s="105"/>
+      <c r="C39" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G39" s="25" t="s">
         <v>165</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>168</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J39" s="28">
+        <v>209</v>
+      </c>
+      <c r="J39" s="26">
         <v>1</v>
       </c>
-      <c r="K39" s="28">
+      <c r="K39" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L39" s="34" t="s">
-        <v>210</v>
+      <c r="L39" s="32" t="s">
+        <v>207</v>
       </c>
       <c r="M39" s="16">
         <v>2.5</v>
       </c>
-      <c r="N39" s="36">
+      <c r="N39" s="34">
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-      <c r="O39" s="61">
+      <c r="O39" s="58">
         <v>2.5</v>
       </c>
-      <c r="P39" s="69">
+      <c r="P39" s="66">
         <f t="shared" si="2"/>
         <v>12.5</v>
       </c>
       <c r="Q39" s="12"/>
     </row>
     <row r="40" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="23">
+      <c r="A40" s="110">
         <v>38</v>
       </c>
-      <c r="B40" s="106"/>
-      <c r="C40" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="D40" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>166</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="B40" s="105"/>
+      <c r="C40" s="83" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="84" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="85" t="s">
+        <v>100</v>
+      </c>
+      <c r="F40" s="85" t="s">
+        <v>163</v>
+      </c>
+      <c r="G40" s="85" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="J40" s="28">
+      <c r="I40" s="109" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40" s="88">
         <v>1</v>
       </c>
-      <c r="K40" s="28">
+      <c r="K40" s="88">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L40" s="34" t="s">
-        <v>210</v>
-      </c>
-      <c r="M40" s="24">
+      <c r="L40" s="89" t="s">
+        <v>207</v>
+      </c>
+      <c r="M40" s="90">
         <v>0.51</v>
       </c>
-      <c r="N40" s="36">
+      <c r="N40" s="47">
         <f t="shared" si="1"/>
         <v>0.51</v>
       </c>
-      <c r="O40" s="61">
+      <c r="O40" s="60">
         <v>0.51</v>
       </c>
-      <c r="P40" s="69">
+      <c r="P40" s="91">
         <f t="shared" si="2"/>
         <v>2.5499999999999998</v>
       </c>
-      <c r="Q40" s="35"/>
+      <c r="Q40" s="92"/>
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="23">
+      <c r="A41" s="110">
         <v>39</v>
       </c>
-      <c r="B41" s="107"/>
-      <c r="C41" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="D41" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="E41" s="45" t="s">
-        <v>180</v>
-      </c>
-      <c r="F41" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="G41" s="45" t="s">
-        <v>174</v>
-      </c>
-      <c r="H41" s="13" t="s">
+      <c r="B41" s="105"/>
+      <c r="C41" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="G41" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="J41" s="46">
+      <c r="I41" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J41" s="26">
         <v>1</v>
       </c>
-      <c r="K41" s="46">
+      <c r="K41" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L41" s="47" t="s">
-        <v>210</v>
-      </c>
-      <c r="M41" s="18">
+      <c r="L41" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="M41" s="22">
         <v>0.4</v>
       </c>
-      <c r="N41" s="48">
+      <c r="N41" s="66">
         <f t="shared" si="1"/>
         <v>0.4</v>
       </c>
-      <c r="O41" s="62">
+      <c r="O41" s="66">
         <v>0.4</v>
       </c>
-      <c r="P41" s="73">
+      <c r="P41" s="66">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="Q41" s="19"/>
+      <c r="Q41" s="33"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="23">
+      <c r="A42" s="110">
         <v>40</v>
       </c>
-      <c r="B42" s="105" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="57" t="s">
-        <v>185</v>
-      </c>
-      <c r="D42" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="F42" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="G42" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="H42" s="30" t="s">
+      <c r="B42" s="106"/>
+      <c r="C42" s="114" t="s">
+        <v>234</v>
+      </c>
+      <c r="D42" s="111" t="s">
+        <v>231</v>
+      </c>
+      <c r="E42" s="112" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" s="112" t="s">
+        <v>232</v>
+      </c>
+      <c r="G42" s="112" t="s">
+        <v>233</v>
+      </c>
+      <c r="H42" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="J42" s="32">
+      <c r="I42" s="116" t="s">
+        <v>209</v>
+      </c>
+      <c r="J42" s="117">
         <v>1</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="117">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="111">
+      <c r="L42" s="113" t="s">
+        <v>207</v>
+      </c>
+      <c r="M42" s="118">
+        <v>0.79</v>
+      </c>
+      <c r="N42" s="45">
+        <f t="shared" si="1"/>
+        <v>0.79</v>
+      </c>
+      <c r="O42" s="59">
+        <v>0.79</v>
+      </c>
+      <c r="P42" s="45">
+        <f t="shared" si="2"/>
+        <v>3.95</v>
+      </c>
+      <c r="Q42" s="119"/>
+    </row>
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="110">
+        <v>41</v>
+      </c>
+      <c r="B43" s="104" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="D43" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="G43" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H43" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="J43" s="30">
+        <v>1</v>
+      </c>
+      <c r="K43" s="30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="98">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O42" s="64"/>
-      <c r="P42" s="111">
+      <c r="O43" s="61"/>
+      <c r="P43" s="98">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q42" s="33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="23">
-        <v>41</v>
-      </c>
-      <c r="B43" s="106"/>
-      <c r="C43" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="D43" s="26" t="s">
+      <c r="Q43" s="31" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="110">
+        <v>42</v>
+      </c>
+      <c r="B44" s="105"/>
+      <c r="C44" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="27" t="s">
+      <c r="E44" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="F43" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="G43" s="28"/>
-      <c r="H43" s="3" t="s">
+      <c r="F44" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="7"/>
-      <c r="J43" s="28">
+      <c r="I44" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J44" s="26">
         <v>1</v>
       </c>
-      <c r="K43" s="28">
+      <c r="K44" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L43" s="28"/>
-      <c r="M43" s="24"/>
-      <c r="N43" s="36">
+      <c r="L44" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="M44" s="22">
+        <v>0</v>
+      </c>
+      <c r="N44" s="34">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="O43" s="61"/>
-      <c r="P43" s="69">
+      <c r="O44" s="58">
+        <v>0</v>
+      </c>
+      <c r="P44" s="66">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q43" s="35"/>
-    </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="23">
-        <v>42</v>
-      </c>
-      <c r="B44" s="106"/>
-      <c r="C44" s="88" t="s">
-        <v>189</v>
-      </c>
-      <c r="D44" s="89" t="s">
-        <v>190</v>
-      </c>
-      <c r="E44" s="90" t="s">
+      <c r="Q44" s="33"/>
+    </row>
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="110">
+        <v>43</v>
+      </c>
+      <c r="B45" s="105"/>
+      <c r="C45" s="83" t="s">
+        <v>186</v>
+      </c>
+      <c r="D45" s="84" t="s">
+        <v>187</v>
+      </c>
+      <c r="E45" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="F44" s="90" t="s">
+      <c r="F45" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="G45" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="G44" s="90" t="s">
-        <v>194</v>
-      </c>
-      <c r="H44" s="91" t="s">
+      <c r="H45" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="I44" s="92"/>
-      <c r="J44" s="93">
+      <c r="I45" s="87" t="s">
+        <v>215</v>
+      </c>
+      <c r="J45" s="88">
         <v>1</v>
       </c>
-      <c r="K44" s="93">
+      <c r="K45" s="88">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L44" s="94" t="s">
-        <v>210</v>
-      </c>
-      <c r="M44" s="95">
+      <c r="L45" s="89" t="s">
+        <v>207</v>
+      </c>
+      <c r="M45" s="90">
         <v>0.14000000000000001</v>
       </c>
-      <c r="N44" s="50">
+      <c r="N45" s="47">
         <f t="shared" si="1"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="O44" s="63">
+      <c r="O45" s="60">
         <v>0.14000000000000001</v>
       </c>
-      <c r="P44" s="96">
+      <c r="P45" s="91">
         <f t="shared" si="2"/>
         <v>0.70000000000000007</v>
       </c>
-      <c r="Q44" s="97"/>
-    </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="23">
-        <v>43</v>
-      </c>
-      <c r="B45" s="106"/>
-      <c r="C45" s="101" t="s">
-        <v>192</v>
-      </c>
-      <c r="D45" s="98" t="s">
-        <v>193</v>
-      </c>
-      <c r="E45" s="99" t="s">
+      <c r="Q45" s="92"/>
+    </row>
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="110">
+        <v>44</v>
+      </c>
+      <c r="B46" s="105"/>
+      <c r="C46" s="96" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" s="93" t="s">
+        <v>190</v>
+      </c>
+      <c r="E46" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="F45" s="99" t="s">
-        <v>214</v>
-      </c>
-      <c r="G45" s="99" t="s">
+      <c r="F46" s="94" t="s">
+        <v>211</v>
+      </c>
+      <c r="G46" s="94" t="s">
         <v>28</v>
       </c>
-      <c r="H45" s="99" t="s">
+      <c r="H46" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="I45" s="100" t="s">
-        <v>218</v>
-      </c>
-      <c r="J45" s="67">
+      <c r="I46" s="95" t="s">
+        <v>215</v>
+      </c>
+      <c r="J46" s="64">
         <v>1</v>
       </c>
-      <c r="K45" s="67">
+      <c r="K46" s="64">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L45" s="100" t="s">
-        <v>210</v>
-      </c>
-      <c r="M45" s="100">
+      <c r="L46" s="95" t="s">
+        <v>207</v>
+      </c>
+      <c r="M46" s="95">
         <v>1.04</v>
       </c>
-      <c r="N45" s="69">
+      <c r="N46" s="66">
         <f t="shared" si="1"/>
         <v>1.04</v>
       </c>
-      <c r="O45" s="110"/>
-      <c r="P45" s="100">
+      <c r="O46" s="97"/>
+      <c r="P46" s="95">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q45" s="113" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23">
-        <v>44</v>
-      </c>
-      <c r="B46" s="107"/>
-      <c r="C46" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="D46" s="52" t="s">
-        <v>207</v>
-      </c>
-      <c r="E46" s="53" t="s">
+      <c r="Q46" s="100" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="110">
+        <v>45</v>
+      </c>
+      <c r="B47" s="106"/>
+      <c r="C47" s="48" t="s">
+        <v>203</v>
+      </c>
+      <c r="D47" s="49" t="s">
+        <v>204</v>
+      </c>
+      <c r="E47" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F46" s="53" t="s">
-        <v>206</v>
-      </c>
-      <c r="G46" s="53" t="s">
+      <c r="F47" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="H46" s="53" t="s">
+      <c r="H47" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="I46" s="55" t="s">
-        <v>212</v>
-      </c>
-      <c r="J46" s="54">
+      <c r="I47" s="52" t="s">
+        <v>209</v>
+      </c>
+      <c r="J47" s="51">
         <v>9</v>
       </c>
-      <c r="K46" s="54">
+      <c r="K47" s="51">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="L46" s="55" t="s">
-        <v>219</v>
-      </c>
-      <c r="M46" s="55" t="s">
-        <v>220</v>
-      </c>
-      <c r="N46" s="59"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="112">
+      <c r="L47" s="52" t="s">
+        <v>216</v>
+      </c>
+      <c r="M47" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="N47" s="56"/>
+      <c r="O47" s="62"/>
+      <c r="P47" s="99">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="Q46" s="56" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="9"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="109" t="s">
-        <v>230</v>
-      </c>
-      <c r="K47" s="109"/>
-      <c r="L47" s="109"/>
-      <c r="M47" s="109"/>
-      <c r="N47" s="10">
-        <f>SUM(N3:N46)</f>
-        <v>41.710999999999991</v>
-      </c>
-      <c r="O47" s="10"/>
-      <c r="P47" s="10"/>
-      <c r="Q47" s="9"/>
-    </row>
-    <row r="48" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="Q47" s="53" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9"/>
       <c r="B48" s="9"/>
       <c r="C48" s="5"/>
@@ -4337,32 +4423,56 @@
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="9"/>
-      <c r="I48" s="20"/>
+      <c r="I48" s="18"/>
       <c r="J48" s="108" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K48" s="108"/>
       <c r="L48" s="108"/>
       <c r="M48" s="108"/>
       <c r="N48" s="10">
-        <f>SUM(P3:P46)</f>
-        <v>181.64000000000001</v>
-      </c>
+        <f>SUM(N3:N47)</f>
+        <v>42.692999999999984</v>
+      </c>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
       <c r="Q48" s="9"/>
+    </row>
+    <row r="49" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="107" t="s">
+        <v>226</v>
+      </c>
+      <c r="K49" s="107"/>
+      <c r="L49" s="107"/>
+      <c r="M49" s="107"/>
+      <c r="N49" s="10">
+        <f>SUM(P3:P47)</f>
+        <v>186.089</v>
+      </c>
+      <c r="Q49" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B43:B47"/>
     <mergeCell ref="B16:B27"/>
+    <mergeCell ref="J49:M49"/>
     <mergeCell ref="J48:M48"/>
-    <mergeCell ref="J47:M47"/>
     <mergeCell ref="B3:B8"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B29:B41"/>
+    <mergeCell ref="B29:B42"/>
   </mergeCells>
-  <conditionalFormatting sqref="Q40:Q44 Q46">
+  <conditionalFormatting sqref="Q40:Q45 Q47">
     <cfRule type="dataBar" priority="30">
       <dataBar>
         <cfvo type="min"/>
@@ -4376,7 +4486,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N46:O46 N3:P44">
+  <conditionalFormatting sqref="N47:O47 N3:P45">
     <cfRule type="dataBar" priority="31">
       <dataBar>
         <cfvo type="min"/>
@@ -4390,7 +4500,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q45">
+  <conditionalFormatting sqref="Q46">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -4404,7 +4514,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N45:O45">
+  <conditionalFormatting sqref="N46:O46">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -4456,13 +4566,14 @@
     <hyperlink ref="L39" r:id="rId35"/>
     <hyperlink ref="L40" r:id="rId36"/>
     <hyperlink ref="L41" r:id="rId37"/>
-    <hyperlink ref="L44" r:id="rId38"/>
-    <hyperlink ref="L45" r:id="rId39"/>
+    <hyperlink ref="L45" r:id="rId38"/>
+    <hyperlink ref="L46" r:id="rId39"/>
     <hyperlink ref="L9" r:id="rId40"/>
     <hyperlink ref="L33" r:id="rId41"/>
+    <hyperlink ref="L42" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId42"/>
+  <pageSetup orientation="portrait" r:id="rId43"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4477,7 +4588,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q40:Q44 Q46</xm:sqref>
+          <xm:sqref>Q40:Q45 Q47</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{FD7B7F04-635F-45FD-9B67-860583781CF2}">
@@ -4490,7 +4601,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N46:O46 N3:P44</xm:sqref>
+          <xm:sqref>N47:O47 N3:P45</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{4455626A-B4BE-4468-9DF8-79445C480C15}">
@@ -4503,7 +4614,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>Q45</xm:sqref>
+          <xm:sqref>Q46</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{44FD6668-4685-47E4-87B8-C6F394E9845F}">
@@ -4516,7 +4627,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N45:O45</xm:sqref>
+          <xm:sqref>N46:O46</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
